--- a/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2019/RHODE_ISLAND_2019.xlsx
+++ b/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2019/RHODE_ISLAND_2019.xlsx
@@ -351,28 +351,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D118"/>
+  <dimension ref="A1:D112"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
@@ -395,6 +395,11 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>Total</t>
@@ -426,9 +431,14 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Comitán de Domínguez</t>
+          <t>Comitán De Domínguez</t>
         </is>
       </c>
       <c r="C5">
@@ -439,6 +449,11 @@
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>Frontera Hidalgo</t>
@@ -452,9 +467,14 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Mazapa de Madero</t>
+          <t>Mazapa De Madero</t>
         </is>
       </c>
       <c r="C7">
@@ -465,6 +485,11 @@
       </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>Reforma</t>
@@ -478,6 +503,11 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>Tecpatán</t>
@@ -491,6 +521,11 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>Total</t>
@@ -506,7 +541,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ciudad de México</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -522,6 +557,11 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
           <t>Azcapotzalco</t>
@@ -535,6 +575,11 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
           <t>Benito Juárez</t>
@@ -548,6 +593,11 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>Cuauhtémoc</t>
@@ -561,6 +611,11 @@
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>Gustavo A. Madero</t>
@@ -574,6 +629,11 @@
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>Iztacalco</t>
@@ -587,6 +647,11 @@
       </c>
     </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>Iztapalapa</t>
@@ -600,6 +665,11 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>Milpa Alta</t>
@@ -613,6 +683,11 @@
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>Tlalpan</t>
@@ -626,6 +701,11 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>Xochimilco</t>
@@ -639,6 +719,11 @@
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>Total</t>
@@ -654,12 +739,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Estado de México</t>
+          <t>Estado De México</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Ecatepec de Morelos</t>
+          <t>Ecatepec De Morelos</t>
         </is>
       </c>
       <c r="C22">
@@ -670,6 +755,11 @@
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>Nezahualcóyotl</t>
@@ -683,9 +773,14 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Tlalnepantla de Baz</t>
+          <t>Tlalnepantla De Baz</t>
         </is>
       </c>
       <c r="C24">
@@ -696,6 +791,11 @@
       </c>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>Total</t>
@@ -716,7 +816,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Apaseo el Alto</t>
+          <t>Apaseo El Alto</t>
         </is>
       </c>
       <c r="C26">
@@ -727,6 +827,11 @@
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>Total</t>
@@ -747,7 +852,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Acapulco de Juárez</t>
+          <t>Acapulco De Juárez</t>
         </is>
       </c>
       <c r="C28">
@@ -758,6 +863,11 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>Ahuacuotzingo</t>
@@ -771,9 +881,14 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ayutla de los Libres</t>
+          <t>Ayutla De Los Libres</t>
         </is>
       </c>
       <c r="C30">
@@ -784,6 +899,11 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>Azoyú</t>
@@ -797,9 +917,14 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Coyuca de Catalán</t>
+          <t>Coyuca De Catalán</t>
         </is>
       </c>
       <c r="C32">
@@ -810,9 +935,14 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Zihuatanejo de Azueta</t>
+          <t>Zihuatanejo De Azueta</t>
         </is>
       </c>
       <c r="C33">
@@ -823,6 +953,11 @@
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>San Luis Acatlán</t>
@@ -836,6 +971,11 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
           <t>Tecoanapa</t>
@@ -849,6 +989,11 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
           <t>Tlapehuala</t>
@@ -862,6 +1007,11 @@
       </c>
     </row>
     <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
           <t>Total</t>
@@ -893,6 +1043,11 @@
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>Chapantongo</t>
@@ -906,6 +1061,11 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>Chilcuautla</t>
@@ -919,6 +1079,11 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>Francisco I. Madero</t>
@@ -932,6 +1097,11 @@
       </c>
     </row>
     <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
           <t>Huichapan</t>
@@ -945,6 +1115,11 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>Ixmiquilpan</t>
@@ -958,6 +1133,11 @@
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
           <t>Metztitlán</t>
@@ -971,9 +1151,14 @@
       </c>
     </row>
     <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Pachuca de Soto</t>
+          <t>Pachuca De Soto</t>
         </is>
       </c>
       <c r="C45">
@@ -984,9 +1169,14 @@
       </c>
     </row>
     <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Tenango de Doria</t>
+          <t>Tenango De Doria</t>
         </is>
       </c>
       <c r="C46">
@@ -997,6 +1187,11 @@
       </c>
     </row>
     <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
           <t>Tlaxcoapan</t>
@@ -1010,9 +1205,14 @@
       </c>
     </row>
     <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Tulancingo de Bravo</t>
+          <t>Tulancingo De Bravo</t>
         </is>
       </c>
       <c r="C48">
@@ -1023,6 +1223,11 @@
       </c>
     </row>
     <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1043,7 +1248,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Cuautitlán de García Barragán</t>
+          <t>Cuautitlán De García Barragán</t>
         </is>
       </c>
       <c r="C50">
@@ -1054,6 +1259,11 @@
       </c>
     </row>
     <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
           <t>Degollado</t>
@@ -1067,9 +1277,14 @@
       </c>
     </row>
     <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Unión de Tula</t>
+          <t>Unión De Tula</t>
         </is>
       </c>
       <c r="C52">
@@ -1080,6 +1295,11 @@
       </c>
     </row>
     <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1111,6 +1331,11 @@
       </c>
     </row>
     <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
           <t>Tuzantla</t>
@@ -1124,6 +1349,11 @@
       </c>
     </row>
     <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1155,6 +1385,11 @@
       </c>
     </row>
     <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1186,9 +1421,14 @@
       </c>
     </row>
     <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>San Nicolás de los Garza</t>
+          <t>San Nicolás De Los Garza</t>
         </is>
       </c>
       <c r="C60">
@@ -1199,6 +1439,11 @@
       </c>
     </row>
     <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1230,9 +1475,14 @@
       </c>
     </row>
     <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>San Pedro y San Pablo Teposcolula</t>
+          <t>San Pedro Y San Pablo Teposcolula</t>
         </is>
       </c>
       <c r="C63">
@@ -1243,6 +1493,11 @@
       </c>
     </row>
     <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
           <t>Santiago Ihuitlán Plumas</t>
@@ -1256,6 +1511,11 @@
       </c>
     </row>
     <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
           <t>Santos Reyes Nopala</t>
@@ -1269,6 +1529,11 @@
       </c>
     </row>
     <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1300,6 +1565,11 @@
       </c>
     </row>
     <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B68" t="inlineStr">
         <is>
           <t>Chignahuapan</t>
@@ -1313,6 +1583,11 @@
       </c>
     </row>
     <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
           <t>Epatlán</t>
@@ -1326,6 +1601,11 @@
       </c>
     </row>
     <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
           <t>Guadalupe Victoria</t>
@@ -1339,6 +1619,11 @@
       </c>
     </row>
     <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
           <t>Huaquechula</t>
@@ -1352,9 +1637,14 @@
       </c>
     </row>
     <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Izúcar de Matamoros</t>
+          <t>Izúcar De Matamoros</t>
         </is>
       </c>
       <c r="C72">
@@ -1365,6 +1655,11 @@
       </c>
     </row>
     <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
           <t>Ocoyucan</t>
@@ -1378,6 +1673,11 @@
       </c>
     </row>
     <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
           <t>Tecomatlán</t>
@@ -1391,6 +1691,11 @@
       </c>
     </row>
     <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
           <t>Vicente Guerrero</t>
@@ -1404,9 +1709,14 @@
       </c>
     </row>
     <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Xochitlán de Vicente Suárez</t>
+          <t>Xochitlán De Vicente Suárez</t>
         </is>
       </c>
       <c r="C76">
@@ -1417,6 +1727,11 @@
       </c>
     </row>
     <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
           <t>Zaragoza</t>
@@ -1430,6 +1745,11 @@
       </c>
     </row>
     <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1461,9 +1781,14 @@
       </c>
     </row>
     <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Jalpan de Serra</t>
+          <t>Jalpan De Serra</t>
         </is>
       </c>
       <c r="C80">
@@ -1474,9 +1799,14 @@
       </c>
     </row>
     <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Landa de Matamoros</t>
+          <t>Landa De Matamoros</t>
         </is>
       </c>
       <c r="C81">
@@ -1487,6 +1817,11 @@
       </c>
     </row>
     <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B82" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1518,6 +1853,11 @@
       </c>
     </row>
     <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B84" t="inlineStr">
         <is>
           <t>Ebano</t>
@@ -1531,6 +1871,11 @@
       </c>
     </row>
     <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B85" t="inlineStr">
         <is>
           <t>Xilitla</t>
@@ -1544,6 +1889,11 @@
       </c>
     </row>
     <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B86" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1575,6 +1925,11 @@
       </c>
     </row>
     <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B88" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1606,6 +1961,11 @@
       </c>
     </row>
     <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B90" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1637,6 +1997,11 @@
       </c>
     </row>
     <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B92" t="inlineStr">
         <is>
           <t>Reynosa</t>
@@ -1650,6 +2015,11 @@
       </c>
     </row>
     <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B93" t="inlineStr">
         <is>
           <t>Tampico</t>
@@ -1663,6 +2033,11 @@
       </c>
     </row>
     <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B94" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1694,6 +2069,11 @@
       </c>
     </row>
     <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B96" t="inlineStr">
         <is>
           <t>Tlaxcala</t>
@@ -1707,6 +2087,11 @@
       </c>
     </row>
     <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B97" t="inlineStr">
         <is>
           <t>Zacatelco</t>
@@ -1720,6 +2105,11 @@
       </c>
     </row>
     <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B98" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1751,6 +2141,11 @@
       </c>
     </row>
     <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B100" t="inlineStr">
         <is>
           <t>Comapa</t>
@@ -1764,6 +2159,11 @@
       </c>
     </row>
     <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B101" t="inlineStr">
         <is>
           <t>Cuitláhuac</t>
@@ -1777,6 +2177,11 @@
       </c>
     </row>
     <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B102" t="inlineStr">
         <is>
           <t>Huatusco</t>
@@ -1790,6 +2195,11 @@
       </c>
     </row>
     <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B103" t="inlineStr">
         <is>
           <t>Juan Rodríguez Clara</t>
@@ -1803,9 +2213,14 @@
       </c>
     </row>
     <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Martínez de la Torre</t>
+          <t>Martínez De La Torre</t>
         </is>
       </c>
       <c r="C104">
@@ -1816,6 +2231,11 @@
       </c>
     </row>
     <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B105" t="inlineStr">
         <is>
           <t>Playa Vicente</t>
@@ -1829,6 +2249,11 @@
       </c>
     </row>
     <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B106" t="inlineStr">
         <is>
           <t>Xalapa</t>
@@ -1842,6 +2267,11 @@
       </c>
     </row>
     <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B107" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1873,6 +2303,11 @@
       </c>
     </row>
     <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Yucatán</t>
+        </is>
+      </c>
       <c r="B109" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1904,6 +2339,11 @@
       </c>
     </row>
     <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B111" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1927,41 +2367,6 @@
       </c>
       <c r="D112">
         <v>1</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 800,811</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Abril de 2020</t>
-        </is>
       </c>
     </row>
   </sheetData>
